--- a/data/trans_bre/IP19C08-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP19C08-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-23,25; 3,94</t>
+          <t>-22,81; 6,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 21,22</t>
+          <t>-1,18; 23,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 3,29</t>
+          <t>-10,0; 3,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,81; 7,38</t>
+          <t>-13,31; 8,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 137,42</t>
+          <t>-100,0; 280,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 7,89</t>
+          <t>-0,96; 7,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 2,84</t>
+          <t>-4,45; 2,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 9,42</t>
+          <t>-2,5; 9,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 4,94</t>
+          <t>-15,72; 4,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 5,98</t>
+          <t>-12,48; 6,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -875,12 +875,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 0,0</t>
+          <t>-5,47; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 139,34</t>
+          <t>-100,0; 123,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 19,78</t>
+          <t>1,37; 20,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 12,55</t>
+          <t>-3,07; 13,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 10,09</t>
+          <t>-4,62; 10,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,09; -1,02</t>
+          <t>-20,06; -0,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-72,95; —</t>
+          <t>-82,6; 808,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,42</t>
+          <t>0,0; 23,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 0,0</t>
+          <t>-11,85; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 6,84</t>
+          <t>-9,61; 7,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,11</t>
+          <t>0,0; 15,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,02; 6,95</t>
+          <t>-13,54; 5,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 18,64</t>
+          <t>-1,53; 17,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 4,59</t>
+          <t>-15,1; 4,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 302,43</t>
+          <t>-100,0; 283,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 7,3</t>
+          <t>-8,26; 7,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 13,06</t>
+          <t>-0,5; 13,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 7,03</t>
+          <t>-8,66; 6,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,75; 3,56</t>
+          <t>-14,77; 2,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-66,84; 166,52</t>
+          <t>-67,97; 161,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-46,28; —</t>
+          <t>-36,68; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-78,46; 322,6</t>
+          <t>-82,48; 226,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 351,51</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 2,12</t>
+          <t>-5,75; 2,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 0,59</t>
+          <t>-7,34; 0,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 7,8</t>
+          <t>-0,17; 7,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 3,63</t>
+          <t>-1,69; 3,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 2,87</t>
+          <t>-1,85; 2,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 3,49</t>
+          <t>-0,93; 3,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 0,86</t>
+          <t>-4,22; 0,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-27,65; 112,01</t>
+          <t>-29,28; 108,92</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-43,37; 104,03</t>
+          <t>-40,03; 101,22</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-29,56; 224,81</t>
+          <t>-26,32; 211,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-78,35; 48,89</t>
+          <t>-76,9; 55,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C08-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP19C08-Provincia-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-22,81; 6,2</t>
+          <t>-21,12; 5,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 23,48</t>
+          <t>-1,25; 22,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 3,22</t>
+          <t>-9,84; 1,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 8,0</t>
+          <t>-13,03; 7,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 280,14</t>
+          <t>-100,0; 198,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 7,76</t>
+          <t>-0,94; 8,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 2,97</t>
+          <t>-4,47; 2,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 9,45</t>
+          <t>-1,96; 10,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-83,58; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 4,99</t>
+          <t>-15,55; 6,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 6,02</t>
+          <t>-12,4; 6,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -875,17 +875,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 0,0</t>
+          <t>-5,5; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 123,2</t>
+          <t>-100,0; 229,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 335,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 20,13</t>
+          <t>1,23; 19,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 13,96</t>
+          <t>-3,13; 13,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 10,22</t>
+          <t>-4,51; 9,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,06; -0,92</t>
+          <t>-17,53; -0,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-82,6; 808,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,86</t>
+          <t>0,0; 20,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 0,0</t>
+          <t>-12,01; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 7,6</t>
+          <t>-9,35; 7,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,24</t>
+          <t>0,0; 16,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 5,57</t>
+          <t>-15,04; 6,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 17,63</t>
+          <t>-0,71; 17,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 4,39</t>
+          <t>-14,04; 4,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 283,21</t>
+          <t>-100,0; 350,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 7,89</t>
+          <t>-8,81; 6,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 13,25</t>
+          <t>-0,57; 13,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 6,46</t>
+          <t>-7,53; 6,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 2,99</t>
+          <t>-13,93; 3,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-67,97; 161,3</t>
+          <t>-66,94; 150,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-36,68; —</t>
+          <t>-48,88; 1048,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-82,48; 226,24</t>
+          <t>-79,95; 261,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 351,51</t>
+          <t>-100,0; 444,96</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 2,25</t>
+          <t>-5,5; 2,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 0,72</t>
+          <t>-7,67; 0,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 7,61</t>
+          <t>-0,2; 7,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 3,8</t>
+          <t>-1,93; 3,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 2,7</t>
+          <t>-1,98; 2,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,36</t>
+          <t>-1,13; 3,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 0,92</t>
+          <t>-4,34; 0,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-29,28; 108,92</t>
+          <t>-32,14; 98,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-40,03; 101,22</t>
+          <t>-39,02; 110,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-26,32; 211,14</t>
+          <t>-31,49; 190,32</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-76,9; 55,14</t>
+          <t>-74,56; 49,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C08-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP19C08-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,36</t>
+          <t>-0,8</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-19,31%</t>
+          <t>-10,85%</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-21,12; 5,08</t>
+          <t>-23,25; 3,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 22,73</t>
+          <t>-1,06; 21,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 1,82</t>
+          <t>-10,42; 3,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 7,24</t>
+          <t>-12,82; 8,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 198,13</t>
+          <t>-100,0; 137,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 8,0</t>
+          <t>-1,0; 7,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 2,97</t>
+          <t>-5,09; 2,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 10,17</t>
+          <t>-2,52; 9,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-83,58; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,05</t>
+          <t>-0,96</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,55; 6,28</t>
+          <t>-14,23; 4,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 6,07</t>
+          <t>-11,15; 5,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -875,17 +875,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 0,0</t>
+          <t>-4,99; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 229,37</t>
+          <t>-100,0; 139,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 335,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-5,62</t>
+          <t>-6,1</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 19,47</t>
+          <t>1,2; 19,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 13,01</t>
+          <t>-2,98; 12,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 9,78</t>
+          <t>-4,7; 10,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,53; -0,91</t>
+          <t>-21,79; -1,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-72,95; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,39</t>
+          <t>-1,53</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-25,58%</t>
+          <t>-29,11%</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,58</t>
+          <t>0,0; 22,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 0,0</t>
+          <t>-10,19; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 7,51</t>
+          <t>-10,1; 6,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-3,12</t>
+          <t>-3,23</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-55,69%</t>
+          <t>-58,61%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,33</t>
+          <t>0,0; 16,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 6,17</t>
+          <t>-15,02; 6,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 17,18</t>
+          <t>-0,69; 18,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,04; 4,75</t>
+          <t>-14,53; 4,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 350,7</t>
+          <t>-100,0; 302,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-2,25</t>
+          <t>-2,61</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-41,59%</t>
+          <t>-45,36%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 6,75</t>
+          <t>-8,3; 7,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 13,3</t>
+          <t>-0,6; 13,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 6,27</t>
+          <t>-7,41; 7,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 3,38</t>
+          <t>-16,42; 3,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-66,94; 150,16</t>
+          <t>-66,84; 166,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-48,88; 1048,13</t>
+          <t>-46,28; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-79,95; 261,13</t>
+          <t>-78,46; 322,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 444,96</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,48</t>
+          <t>2,54</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>433,34%</t>
+          <t>656,31%</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 2,6</t>
+          <t>-5,8; 2,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 0,65</t>
+          <t>-7,24; 0,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 7,47</t>
+          <t>0,0; 7,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1,17</t>
+          <t>-1,19</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-34,5%</t>
+          <t>-35,39%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 3,47</t>
+          <t>-1,57; 3,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 2,68</t>
+          <t>-2,2; 2,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 3,23</t>
+          <t>-0,98; 3,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 0,9</t>
+          <t>-4,98; 0,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-32,14; 98,14</t>
+          <t>-27,65; 112,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-39,02; 110,87</t>
+          <t>-43,37; 104,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-31,49; 190,32</t>
+          <t>-29,56; 224,81</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-74,56; 49,21</t>
+          <t>-80,66; 46,59</t>
         </is>
       </c>
     </row>
